--- a/public/Master Style.xlsx
+++ b/public/Master Style.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="128">
   <si>
     <t>No</t>
   </si>
@@ -44,490 +44,376 @@
     <t>Style Name</t>
   </si>
   <si>
-    <t>B00001</t>
-  </si>
-  <si>
-    <t>S00001</t>
+    <t>Style Desc</t>
+  </si>
+  <si>
+    <t>BRN000000001</t>
+  </si>
+  <si>
+    <t>STY000000001</t>
   </si>
   <si>
     <t>WC11K046RS/RS1</t>
   </si>
   <si>
-    <t>S00002</t>
+    <t>Example of style desc</t>
+  </si>
+  <si>
+    <t>STY000000002</t>
   </si>
   <si>
     <t>WC11K046ES/ES1</t>
   </si>
   <si>
-    <t>S00003</t>
+    <t>STY000000003</t>
   </si>
   <si>
     <t>WC11K046PS/PS1</t>
   </si>
   <si>
-    <t>S00004</t>
+    <t>STY000000004</t>
   </si>
   <si>
     <t>WC10K004R WC44K004R</t>
   </si>
   <si>
-    <t>S00005</t>
+    <t>STY000000005</t>
   </si>
   <si>
     <t>WC10K004ES/ES1</t>
   </si>
   <si>
-    <t>S00006</t>
+    <t>STY000000006</t>
   </si>
   <si>
     <t>WC10K004P WC44K004P</t>
   </si>
   <si>
-    <t>S00007</t>
+    <t>STY000000007</t>
   </si>
   <si>
     <t>WC10K010R WC44K010R</t>
   </si>
   <si>
-    <t>S00008</t>
+    <t>STY000000008</t>
   </si>
   <si>
     <t>WC43K001RS</t>
   </si>
   <si>
-    <t>S00009</t>
+    <t>STY000000009</t>
   </si>
   <si>
     <t>WC43K001ES</t>
   </si>
   <si>
-    <t>S00010</t>
+    <t>STY000000010</t>
   </si>
   <si>
     <t>WC43K001PS</t>
   </si>
   <si>
-    <t>S00011</t>
+    <t>STY000000011</t>
   </si>
   <si>
     <t>WC43K001RN/RP</t>
   </si>
   <si>
-    <t>S00012</t>
+    <t>STY000000012</t>
   </si>
   <si>
     <t>WC43K001EN/EP</t>
   </si>
   <si>
-    <t>S00013</t>
+    <t>STY000000013</t>
   </si>
   <si>
     <t>WC43K001PN/PP</t>
   </si>
   <si>
-    <t>S00014</t>
+    <t>STY000000014</t>
   </si>
   <si>
     <t>WC43K001RR</t>
   </si>
   <si>
-    <t>S00015</t>
+    <t>STY000000015</t>
   </si>
   <si>
     <t>WC43K001ER</t>
   </si>
   <si>
-    <t>S00016</t>
+    <t>STY000000016</t>
   </si>
   <si>
     <t>WC43K001PR</t>
   </si>
   <si>
-    <t>S00017</t>
+    <t>STY000000017</t>
   </si>
   <si>
     <t>WC43K012RR</t>
   </si>
   <si>
-    <t>S00018</t>
+    <t>STY000000018</t>
   </si>
   <si>
     <t>WC43K012ER</t>
   </si>
   <si>
-    <t>S00019</t>
+    <t>STY000000019</t>
   </si>
   <si>
     <t>WC43K012PR</t>
   </si>
   <si>
-    <t>S00020</t>
+    <t>STY000000020</t>
   </si>
   <si>
     <t>WC43K012RP</t>
   </si>
   <si>
-    <t>S00021</t>
+    <t>STY000000021</t>
   </si>
   <si>
     <t>WC43K012EP/EN</t>
   </si>
   <si>
-    <t>S00022</t>
+    <t>STY000000022</t>
   </si>
   <si>
     <t>WC43K012PP</t>
   </si>
   <si>
-    <t>S00023</t>
+    <t>STY000000023</t>
   </si>
   <si>
     <t>WC11K034RS/RS1</t>
   </si>
   <si>
-    <t>S00024</t>
+    <t>STY000000024</t>
   </si>
   <si>
     <t>WC11K034ES/ES1</t>
   </si>
   <si>
-    <t>S00025</t>
+    <t>STY000000025</t>
   </si>
   <si>
     <t>WC11K034PS/PS1</t>
   </si>
   <si>
-    <t>S00026</t>
+    <t>STY000000026</t>
   </si>
   <si>
     <t>WC43K012RS</t>
   </si>
   <si>
-    <t>S00027</t>
+    <t>STY000000027</t>
   </si>
   <si>
     <t>WC43K012ES</t>
   </si>
   <si>
-    <t>S00028</t>
+    <t>STY000000028</t>
   </si>
   <si>
     <t>WC43K012PS</t>
   </si>
   <si>
-    <t>S00029</t>
+    <t>STY000000029</t>
   </si>
   <si>
     <t>WC44K004RR1</t>
   </si>
   <si>
-    <t>S00030</t>
+    <t>STY000000030</t>
   </si>
   <si>
     <t>WC44K010RR1</t>
   </si>
   <si>
-    <t>S00031</t>
+    <t>STY000000031</t>
   </si>
   <si>
     <t>WC44K004RP1/RN1</t>
   </si>
   <si>
-    <t>S00032</t>
+    <t>STY000000032</t>
   </si>
   <si>
     <t>WC44K004EP1/EN1</t>
   </si>
   <si>
-    <t>S00033</t>
+    <t>STY000000033</t>
   </si>
   <si>
     <t>WC44K004PP1/PN1</t>
   </si>
   <si>
-    <t>S00034</t>
+    <t>STY000000034</t>
   </si>
   <si>
     <t>WC44K010RP1/RN1</t>
   </si>
   <si>
-    <t>S00035</t>
+    <t>STY000000035</t>
   </si>
   <si>
     <t>WC44K010PP1/PN1</t>
   </si>
   <si>
-    <t>S00036</t>
+    <t>STY000000036</t>
   </si>
   <si>
     <t>WC44K004RS</t>
   </si>
   <si>
-    <t>S00037</t>
+    <t>STY000000037</t>
   </si>
   <si>
     <t>WC44K004ES</t>
   </si>
   <si>
-    <t>S00038</t>
+    <t>STY000000038</t>
   </si>
   <si>
     <t>WC44K004PS</t>
   </si>
   <si>
-    <t>S00039</t>
+    <t>STY000000039</t>
   </si>
   <si>
     <t>WC44K010RS</t>
   </si>
   <si>
-    <t>S00040</t>
+    <t>STY000000040</t>
   </si>
   <si>
     <t>WC44K010PS</t>
   </si>
   <si>
-    <t>S00041</t>
+    <t>STY000000041</t>
   </si>
   <si>
     <t>WC44K004PR1</t>
   </si>
   <si>
-    <t>S00042</t>
+    <t>STY000000042</t>
   </si>
   <si>
     <t>WC44K010ER1</t>
   </si>
   <si>
-    <t>S00043</t>
+    <t>STY000000043</t>
   </si>
   <si>
     <t>WC44K010EP1/EN1</t>
   </si>
   <si>
-    <t>S00044</t>
+    <t>STY000000044</t>
   </si>
   <si>
     <t>WC10K004RS/RS1</t>
   </si>
   <si>
-    <t>S00045</t>
+    <t>STY000000045</t>
   </si>
   <si>
     <t>WC10K004PS/PS1</t>
   </si>
   <si>
-    <t>S00046</t>
+    <t>STY000000046</t>
   </si>
   <si>
     <t>WC10K010RS/RS1</t>
   </si>
   <si>
-    <t>S00047</t>
+    <t>STY000000047</t>
   </si>
   <si>
     <t>WC10K010ES/ES1</t>
   </si>
   <si>
-    <t>S00048</t>
+    <t>STY000000048</t>
   </si>
   <si>
     <t>WC10K010PS/PS1</t>
   </si>
   <si>
-    <t>S00049</t>
+    <t>STY000000049</t>
   </si>
   <si>
     <t>WC51K004RS</t>
   </si>
   <si>
-    <t>S00050</t>
+    <t>STY000000050</t>
   </si>
   <si>
     <t>WC51K010RS</t>
   </si>
   <si>
-    <t>S00051</t>
+    <t>STY000000051</t>
   </si>
   <si>
     <t>WC51K004RR</t>
   </si>
   <si>
-    <t>S00052</t>
+    <t>STY000000052</t>
   </si>
   <si>
     <t>WC51K004PR</t>
   </si>
   <si>
-    <t>S00053</t>
+    <t>STY000000053</t>
   </si>
   <si>
     <t>WC51K010RR</t>
   </si>
   <si>
-    <t>S00054</t>
+    <t>STY000000054</t>
   </si>
   <si>
     <t>WC51K004RG</t>
   </si>
   <si>
-    <t>S00055</t>
+    <t>STY000000055</t>
   </si>
   <si>
     <t>WC51K004PG</t>
   </si>
   <si>
-    <t>B00002</t>
-  </si>
-  <si>
-    <t>S00056</t>
+    <t>BRN000000002</t>
+  </si>
+  <si>
+    <t>STY000000056</t>
   </si>
   <si>
     <t>MA43K100</t>
   </si>
   <si>
-    <t>S00057</t>
+    <t>STY000000057</t>
   </si>
   <si>
     <t>MA73K160RS1_RS2</t>
   </si>
   <si>
-    <t>S00058</t>
+    <t>STY000000058</t>
   </si>
   <si>
     <t>MA73K161RS1_RS2</t>
   </si>
   <si>
-    <t>S00059</t>
+    <t>STY000000059</t>
   </si>
   <si>
     <t>MA61K999XS1_XS2</t>
   </si>
   <si>
-    <t>S00060</t>
+    <t>STY000000060</t>
   </si>
   <si>
     <t>MA61K998RS1-RS2</t>
-  </si>
-  <si>
-    <t>B00019</t>
-  </si>
-  <si>
-    <t>S00061</t>
-  </si>
-  <si>
-    <t>UJ42J200</t>
-  </si>
-  <si>
-    <t>B00010</t>
-  </si>
-  <si>
-    <t>S00062</t>
-  </si>
-  <si>
-    <t>B00011</t>
-  </si>
-  <si>
-    <t>S00063</t>
-  </si>
-  <si>
-    <t>B00012</t>
-  </si>
-  <si>
-    <t>S00064</t>
-  </si>
-  <si>
-    <t>B00013</t>
-  </si>
-  <si>
-    <t>S00065</t>
-  </si>
-  <si>
-    <t>S00066</t>
-  </si>
-  <si>
-    <t>S00067</t>
-  </si>
-  <si>
-    <t>S00068</t>
-  </si>
-  <si>
-    <t>S00069</t>
-  </si>
-  <si>
-    <t>S00070</t>
-  </si>
-  <si>
-    <t>S00071</t>
-  </si>
-  <si>
-    <t>B00005</t>
-  </si>
-  <si>
-    <t>S00072</t>
-  </si>
-  <si>
-    <t>S00073</t>
-  </si>
-  <si>
-    <t>S00074</t>
-  </si>
-  <si>
-    <t>S00075</t>
-  </si>
-  <si>
-    <t>S00076</t>
-  </si>
-  <si>
-    <t>S00077</t>
-  </si>
-  <si>
-    <t>B00004</t>
-  </si>
-  <si>
-    <t>S00078</t>
-  </si>
-  <si>
-    <t>B00006</t>
-  </si>
-  <si>
-    <t>S00079</t>
-  </si>
-  <si>
-    <t>S00080</t>
-  </si>
-  <si>
-    <t>S00081</t>
-  </si>
-  <si>
-    <t>S00082</t>
-  </si>
-  <si>
-    <t>S00083</t>
-  </si>
-  <si>
-    <t>S00084</t>
-  </si>
-  <si>
-    <t>S00085</t>
-  </si>
-  <si>
-    <t>B00007</t>
-  </si>
-  <si>
-    <t>S00086</t>
-  </si>
-  <si>
-    <t>S00087</t>
-  </si>
-  <si>
-    <t>S00088</t>
-  </si>
-  <si>
-    <t>S00089</t>
-  </si>
-  <si>
-    <t>S00090</t>
   </si>
 </sst>
 </file>
@@ -1463,13 +1349,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D91"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
+  <dimension ref="A1:E61"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="14.2857142857143" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.1428571428571" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5714285714286" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1482,1274 +1373,854 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>20</v>
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>22</v>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" t="s">
-        <v>26</v>
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" t="s">
-        <v>28</v>
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>30</v>
+      <c r="B14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" t="s">
-        <v>32</v>
+      <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" t="s">
-        <v>34</v>
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" t="s">
-        <v>36</v>
+      <c r="B17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" t="s">
-        <v>38</v>
+      <c r="B18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" t="s">
-        <v>40</v>
+      <c r="B19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" t="s">
-        <v>42</v>
+      <c r="B20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" t="s">
-        <v>44</v>
+      <c r="B21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" t="s">
-        <v>46</v>
+      <c r="B22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" t="s">
-        <v>48</v>
+      <c r="B23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" t="s">
-        <v>50</v>
+      <c r="B24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" t="s">
-        <v>52</v>
+      <c r="B25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" t="s">
-        <v>54</v>
+      <c r="B26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" t="s">
-        <v>56</v>
+      <c r="B27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" t="s">
-        <v>58</v>
+      <c r="B28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29" t="s">
-        <v>60</v>
+      <c r="B29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D30" t="s">
-        <v>62</v>
+      <c r="B30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>4</v>
-      </c>
-      <c r="C31" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31" t="s">
-        <v>64</v>
+      <c r="B31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" t="s">
-        <v>66</v>
+      <c r="B32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" t="s">
-        <v>68</v>
+      <c r="B33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" t="s">
-        <v>69</v>
-      </c>
-      <c r="D34" t="s">
-        <v>70</v>
+      <c r="B34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>4</v>
-      </c>
-      <c r="C35" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" t="s">
-        <v>72</v>
+      <c r="B35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>4</v>
-      </c>
-      <c r="C36" t="s">
-        <v>73</v>
-      </c>
-      <c r="D36" t="s">
-        <v>74</v>
+      <c r="B36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
-        <v>4</v>
-      </c>
-      <c r="C37" t="s">
-        <v>75</v>
-      </c>
-      <c r="D37" t="s">
-        <v>76</v>
+      <c r="B37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" t="s">
-        <v>77</v>
-      </c>
-      <c r="D38" t="s">
-        <v>78</v>
+      <c r="B38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" t="s">
-        <v>79</v>
-      </c>
-      <c r="D39" t="s">
-        <v>80</v>
+      <c r="B39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>4</v>
-      </c>
-      <c r="C40" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" t="s">
-        <v>82</v>
+      <c r="B40" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
-        <v>4</v>
-      </c>
-      <c r="C41" t="s">
-        <v>83</v>
-      </c>
-      <c r="D41" t="s">
-        <v>84</v>
+      <c r="B41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>4</v>
-      </c>
-      <c r="C42" t="s">
-        <v>85</v>
-      </c>
-      <c r="D42" t="s">
-        <v>86</v>
+      <c r="B42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" t="s">
-        <v>87</v>
-      </c>
-      <c r="D43" t="s">
-        <v>88</v>
+      <c r="B43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
-        <v>4</v>
-      </c>
-      <c r="C44" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" t="s">
-        <v>90</v>
+      <c r="B44" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
-        <v>4</v>
-      </c>
-      <c r="C45" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" t="s">
-        <v>92</v>
+      <c r="B45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
-        <v>4</v>
-      </c>
-      <c r="C46" t="s">
-        <v>93</v>
-      </c>
-      <c r="D46" t="s">
-        <v>94</v>
+      <c r="B46" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" t="s">
-        <v>95</v>
-      </c>
-      <c r="D47" t="s">
-        <v>96</v>
+      <c r="B47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
-        <v>4</v>
-      </c>
-      <c r="C48" t="s">
-        <v>97</v>
-      </c>
-      <c r="D48" t="s">
-        <v>98</v>
+      <c r="B48" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
-        <v>4</v>
-      </c>
-      <c r="C49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D49" t="s">
-        <v>100</v>
+      <c r="B49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
-        <v>4</v>
-      </c>
-      <c r="C50" t="s">
-        <v>101</v>
-      </c>
-      <c r="D50" t="s">
-        <v>102</v>
+      <c r="B50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" t="s">
-        <v>103</v>
-      </c>
-      <c r="D51" t="s">
-        <v>104</v>
+      <c r="B51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
-        <v>4</v>
-      </c>
-      <c r="C52" t="s">
-        <v>105</v>
-      </c>
-      <c r="D52" t="s">
-        <v>106</v>
+      <c r="B52" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
-        <v>4</v>
-      </c>
-      <c r="C53" t="s">
-        <v>107</v>
-      </c>
-      <c r="D53" t="s">
-        <v>108</v>
+      <c r="B53" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
-        <v>4</v>
-      </c>
-      <c r="C54" t="s">
-        <v>109</v>
-      </c>
-      <c r="D54" t="s">
-        <v>110</v>
+      <c r="B54" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" t="s">
-        <v>111</v>
-      </c>
-      <c r="D55" t="s">
-        <v>112</v>
+      <c r="B55" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
-        <v>4</v>
-      </c>
-      <c r="C56" t="s">
-        <v>113</v>
-      </c>
-      <c r="D56" t="s">
-        <v>114</v>
+      <c r="B56" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
-        <v>115</v>
-      </c>
-      <c r="C57" t="s">
-        <v>116</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="B57" s="1" t="s">
         <v>117</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
-        <v>115</v>
-      </c>
-      <c r="C58" t="s">
-        <v>118</v>
-      </c>
-      <c r="D58" t="s">
-        <v>119</v>
+      <c r="B58" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
-        <v>115</v>
-      </c>
-      <c r="C59" t="s">
-        <v>120</v>
-      </c>
-      <c r="D59" t="s">
-        <v>121</v>
+      <c r="B59" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
-        <v>115</v>
-      </c>
-      <c r="C60" t="s">
-        <v>122</v>
-      </c>
-      <c r="D60" t="s">
-        <v>123</v>
+      <c r="B60" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
-        <v>115</v>
-      </c>
-      <c r="C61" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="1">
-        <v>61</v>
-      </c>
-      <c r="B62" t="s">
+      <c r="B61" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D61" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D62" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="1">
-        <v>62</v>
-      </c>
-      <c r="B63" t="s">
-        <v>129</v>
-      </c>
-      <c r="C63" t="s">
-        <v>130</v>
-      </c>
-      <c r="D63">
-        <v>303302</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="1">
-        <v>63</v>
-      </c>
-      <c r="B64" t="s">
-        <v>131</v>
-      </c>
-      <c r="C64" t="s">
-        <v>132</v>
-      </c>
-      <c r="D64">
-        <v>303302</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="1">
-        <v>64</v>
-      </c>
-      <c r="B65" t="s">
-        <v>133</v>
-      </c>
-      <c r="C65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D65">
-        <v>303302</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="1">
-        <v>65</v>
-      </c>
-      <c r="B66" t="s">
-        <v>135</v>
-      </c>
-      <c r="C66" t="s">
-        <v>136</v>
-      </c>
-      <c r="D66">
-        <v>303302</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="1">
-        <v>66</v>
-      </c>
-      <c r="B67" t="s">
-        <v>129</v>
-      </c>
-      <c r="C67" t="s">
-        <v>137</v>
-      </c>
-      <c r="D67">
-        <v>307630</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="1">
-        <v>67</v>
-      </c>
-      <c r="B68" t="s">
-        <v>135</v>
-      </c>
-      <c r="C68" t="s">
-        <v>138</v>
-      </c>
-      <c r="D68">
-        <v>307630</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="1">
-        <v>68</v>
-      </c>
-      <c r="B69" t="s">
-        <v>129</v>
-      </c>
-      <c r="C69" t="s">
-        <v>139</v>
-      </c>
-      <c r="D69">
-        <v>328943</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="1">
-        <v>69</v>
-      </c>
-      <c r="B70" t="s">
-        <v>133</v>
-      </c>
-      <c r="C70" t="s">
-        <v>140</v>
-      </c>
-      <c r="D70">
-        <v>328943</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="1">
-        <v>70</v>
-      </c>
-      <c r="B71" t="s">
-        <v>135</v>
-      </c>
-      <c r="C71" t="s">
-        <v>141</v>
-      </c>
-      <c r="D71">
-        <v>328943</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="1">
-        <v>71</v>
-      </c>
-      <c r="B72" t="s">
-        <v>129</v>
-      </c>
-      <c r="C72" t="s">
-        <v>142</v>
-      </c>
-      <c r="D72">
-        <v>342935</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="1">
-        <v>72</v>
-      </c>
-      <c r="B73" t="s">
-        <v>143</v>
-      </c>
-      <c r="C73" t="s">
-        <v>144</v>
-      </c>
-      <c r="D73">
-        <v>342935</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="1">
-        <v>73</v>
-      </c>
-      <c r="B74" t="s">
-        <v>129</v>
-      </c>
-      <c r="C74" t="s">
-        <v>145</v>
-      </c>
-      <c r="D74">
-        <v>329344</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="1">
-        <v>74</v>
-      </c>
-      <c r="B75" t="s">
-        <v>131</v>
-      </c>
-      <c r="C75" t="s">
-        <v>146</v>
-      </c>
-      <c r="D75">
-        <v>329344</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="1">
-        <v>75</v>
-      </c>
-      <c r="B76" t="s">
-        <v>133</v>
-      </c>
-      <c r="C76" t="s">
-        <v>147</v>
-      </c>
-      <c r="D76">
-        <v>329344</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" s="1">
-        <v>76</v>
-      </c>
-      <c r="B77" t="s">
-        <v>135</v>
-      </c>
-      <c r="C77" t="s">
-        <v>148</v>
-      </c>
-      <c r="D77">
-        <v>329344</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" s="1">
-        <v>77</v>
-      </c>
-      <c r="B78" t="s">
-        <v>135</v>
-      </c>
-      <c r="C78" t="s">
-        <v>149</v>
-      </c>
-      <c r="D78">
-        <v>342937</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="1">
-        <v>78</v>
-      </c>
-      <c r="B79" t="s">
-        <v>150</v>
-      </c>
-      <c r="C79" t="s">
-        <v>151</v>
-      </c>
-      <c r="D79">
-        <v>619919</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="1">
-        <v>79</v>
-      </c>
-      <c r="B80" t="s">
-        <v>152</v>
-      </c>
-      <c r="C80" t="s">
-        <v>153</v>
-      </c>
-      <c r="D80">
-        <v>544340</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="1">
-        <v>80</v>
-      </c>
-      <c r="B81" t="s">
-        <v>152</v>
-      </c>
-      <c r="C81" t="s">
-        <v>154</v>
-      </c>
-      <c r="D81">
-        <v>619919</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="1">
-        <v>81</v>
-      </c>
-      <c r="B82" t="s">
-        <v>152</v>
-      </c>
-      <c r="C82" t="s">
-        <v>155</v>
-      </c>
-      <c r="D82">
-        <v>693035</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="1">
-        <v>82</v>
-      </c>
-      <c r="B83" t="s">
-        <v>152</v>
-      </c>
-      <c r="C83" t="s">
-        <v>156</v>
-      </c>
-      <c r="D83">
-        <v>693086</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="1">
-        <v>83</v>
-      </c>
-      <c r="B84" t="s">
-        <v>152</v>
-      </c>
-      <c r="C84" t="s">
-        <v>157</v>
-      </c>
-      <c r="D84">
-        <v>421441</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="1">
-        <v>84</v>
-      </c>
-      <c r="B85" t="s">
-        <v>152</v>
-      </c>
-      <c r="C85" t="s">
-        <v>158</v>
-      </c>
-      <c r="D85">
-        <v>567558</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="1">
-        <v>85</v>
-      </c>
-      <c r="B86" t="s">
-        <v>152</v>
-      </c>
-      <c r="C86" t="s">
-        <v>159</v>
-      </c>
-      <c r="D86">
-        <v>601798</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" s="1">
-        <v>86</v>
-      </c>
-      <c r="B87" t="s">
-        <v>160</v>
-      </c>
-      <c r="C87" t="s">
-        <v>161</v>
-      </c>
-      <c r="D87">
-        <v>878746</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="1">
-        <v>87</v>
-      </c>
-      <c r="B88" t="s">
-        <v>160</v>
-      </c>
-      <c r="C88" t="s">
-        <v>162</v>
-      </c>
-      <c r="D88">
-        <v>881293</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="1">
-        <v>88</v>
-      </c>
-      <c r="B89" t="s">
-        <v>160</v>
-      </c>
-      <c r="C89" t="s">
-        <v>163</v>
-      </c>
-      <c r="D89">
-        <v>705130</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="1">
-        <v>89</v>
-      </c>
-      <c r="B90" t="s">
-        <v>160</v>
-      </c>
-      <c r="C90" t="s">
-        <v>164</v>
-      </c>
-      <c r="D90">
-        <v>705131</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" s="1">
-        <v>90</v>
-      </c>
-      <c r="B91" t="s">
-        <v>160</v>
-      </c>
-      <c r="C91" t="s">
-        <v>165</v>
-      </c>
-      <c r="D91">
-        <v>845865</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D19">
-    <sortState ref="A1:D19">
-      <sortCondition ref="A1"/>
-    </sortState>
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
